--- a/artfynd/Breviksnäs artfynd.xlsx
+++ b/artfynd/Breviksnäs artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY365"/>
+  <dimension ref="A1:AZ365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85056781</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126603393</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,6 +1053,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124084</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1165,6 +1185,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753792</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910904</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1404,6 +1434,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124083</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1516,6 +1551,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910903</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1638,6 +1678,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944679</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1765,6 +1810,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124082</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1867,6 +1917,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353738</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1985,6 +2040,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99459342</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2092,6 +2152,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866846</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2204,6 +2269,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910892</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2311,6 +2381,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353704</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2423,6 +2498,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910891</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2520,6 +2600,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131854006</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2627,6 +2712,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365751</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2734,6 +2824,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944681</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2851,6 +2946,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104318857</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2966,6 +3066,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104318910</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3088,6 +3193,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910899</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3210,6 +3320,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910900</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3311,6 +3426,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353710</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3412,6 +3532,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353721</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3520,6 +3645,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98982557</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3628,6 +3758,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98983758</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3745,6 +3880,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98983822</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3862,6 +4002,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99460310</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3959,6 +4104,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99477053</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4076,6 +4226,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104318879</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4193,6 +4348,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104321044</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4310,6 +4470,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104321278</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4432,6 +4597,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944680</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4554,6 +4724,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944684</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4681,6 +4856,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910895</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4788,6 +4968,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124073</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4905,6 +5090,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104321078</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5012,6 +5202,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910898</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5120,6 +5315,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98982342</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5228,6 +5428,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98982525</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5340,6 +5545,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98984020</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5437,6 +5647,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99477051</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5559,6 +5774,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944683</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5674,6 +5894,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126603618</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5784,6 +6009,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126603707</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5894,6 +6124,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126603803</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6021,6 +6256,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753791</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6123,6 +6363,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99477054</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6235,6 +6480,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866844</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6347,6 +6597,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866845</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6457,6 +6712,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131869764</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6589,6 +6849,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753779</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6716,6 +6981,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753789</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6843,6 +7113,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753790</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6975,6 +7250,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866843</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7082,6 +7362,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354473</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7214,6 +7499,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124080</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7346,6 +7636,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124081</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7458,6 +7753,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637912</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7570,6 +7870,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637936</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7682,6 +7987,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637937</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7794,6 +8104,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637913</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7906,6 +8221,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637938</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8018,6 +8338,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104319084</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8130,6 +8455,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637918</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8242,6 +8572,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637943</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8354,6 +8689,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637908</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8466,6 +8806,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637905</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8578,6 +8923,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637933</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8690,6 +9040,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637927</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8802,6 +9157,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637926</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8914,6 +9274,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637952</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9021,6 +9386,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353774</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9133,6 +9503,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944652</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9265,6 +9640,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124079</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9392,6 +9772,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231764</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9514,6 +9899,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944678</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9641,6 +10031,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365753</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9763,6 +10158,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910897</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9890,6 +10290,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910901</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10022,6 +10427,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910893</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10134,6 +10544,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637928</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10255,6 +10670,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128274696</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10369,6 +10789,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97592839</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10478,6 +10903,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99461686</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10602,6 +11032,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99462175</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10704,6 +11139,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99477069</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10815,6 +11255,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126607356</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10922,6 +11367,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944651</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11033,6 +11483,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121224447</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11140,6 +11595,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231765</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11237,6 +11697,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131853396</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11344,6 +11809,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944649</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11456,6 +11926,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944653</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11567,6 +12042,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99462632</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11703,6 +12183,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231767</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11818,6 +12303,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354716</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11946,6 +12436,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97371838</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12055,6 +12550,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98156324</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12161,6 +12661,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353845</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12268,6 +12773,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753764</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12375,6 +12885,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126551318</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12482,6 +12997,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354362</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12589,6 +13109,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354275</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12696,6 +13221,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126551287</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12803,6 +13333,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944654</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12910,6 +13445,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944657</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13037,6 +13577,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231766</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13144,6 +13689,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753771</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13251,6 +13801,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753772</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13352,6 +13907,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128539518</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13459,6 +14019,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365722</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13580,6 +14145,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128280496</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13701,6 +14271,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128280607</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13808,6 +14383,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944647</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13909,6 +14489,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128538845</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14030,6 +14615,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124185384</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14148,6 +14738,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126608529</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14245,6 +14840,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129516551</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14342,6 +14942,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129516552</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14439,6 +15044,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129516553</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14545,6 +15155,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129516554</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14646,6 +15261,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129516555</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14751,6 +15371,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129667335</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14856,6 +15481,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129667428</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14966,6 +15596,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99458070</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15076,6 +15711,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126608100</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15186,6 +15826,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126608423</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15296,6 +15941,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126609668</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15403,6 +16053,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126607980</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15522,6 +16177,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129518124</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15634,6 +16294,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866838</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15746,6 +16411,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866840</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15858,6 +16528,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866841</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15970,6 +16645,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866842</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16089,6 +16769,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866839</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16222,6 +16907,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129516558</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16349,6 +17039,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753768</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16456,6 +17151,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354603</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16572,6 +17272,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126698890</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16704,6 +17409,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753769</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16814,6 +17524,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354555</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16933,6 +17648,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129518152</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17040,6 +17760,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354607</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17147,6 +17872,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121224002</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17263,6 +17993,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126608030</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17380,6 +18115,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133328061</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17497,6 +18237,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133328062</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17614,6 +18359,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133328063</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17719,6 +18469,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129667342</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17826,6 +18581,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126551316</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17933,6 +18693,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231762</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18042,6 +18807,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98156759</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18156,6 +18926,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98156914</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18269,6 +19044,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98156997</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18381,6 +19161,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104336481</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18488,6 +19273,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944645</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18595,6 +19385,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944646</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18698,6 +19493,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354291</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18809,6 +19609,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121224119</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18920,6 +19725,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121224726</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19032,6 +19842,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753773</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19139,6 +19954,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126551299</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19255,6 +20075,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104335875</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19364,6 +20189,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354632</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19489,6 +20319,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98157189</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19596,6 +20431,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944644</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19716,6 +20556,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121330721</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19843,6 +20688,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944687</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19953,6 +20803,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98984862</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20080,6 +20935,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944686</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20187,6 +21047,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124086</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20314,6 +21179,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124070</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20441,6 +21311,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365737</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20547,6 +21422,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131847129</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20669,6 +21549,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124059</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20796,6 +21681,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124064</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20898,6 +21788,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97355018</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21005,6 +21900,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124056</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21112,6 +22012,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124058</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21219,6 +22124,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124061</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21326,6 +22236,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365743</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21433,6 +22348,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910886</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21530,6 +22450,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131847315</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21627,6 +22552,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131848310</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21734,6 +22664,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866851</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21841,6 +22776,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866854</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21938,6 +22878,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131851419</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22045,6 +22990,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124067</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22172,6 +23122,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124071</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22299,6 +23254,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365738</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22426,6 +23386,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124053</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22553,6 +23518,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365739</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22660,6 +23630,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910890</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22786,6 +23761,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128274021</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22893,6 +23873,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365746</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22994,6 +23979,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129516559</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -23101,6 +24091,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866855</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23222,6 +24217,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128277415</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23349,6 +24349,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910887</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23447,6 +24452,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131888521</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23554,6 +24564,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124055</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23668,6 +24683,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129667711</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23775,6 +24795,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910888</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23872,6 +24897,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99477050</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23969,6 +24999,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99477052</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -24114,6 +25149,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99505825</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -24224,6 +25264,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126604532</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -24331,6 +25376,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126604714</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24441,6 +25491,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126604740</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24538,6 +25593,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131848306</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24640,6 +25700,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99477055</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24747,6 +25812,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124060</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24864,6 +25934,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124075</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24981,6 +26056,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753788</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -25093,6 +26173,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866847</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -25205,6 +26290,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866848</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -25317,6 +26407,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866856</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25429,6 +26524,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866857</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25526,6 +26626,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131888523</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25638,6 +26743,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353544</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25775,6 +26885,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124066</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25902,6 +27017,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124072</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -26034,6 +27154,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124078</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -26166,6 +27291,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753786</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26298,6 +27428,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365742</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26430,6 +27565,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944675</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26562,6 +27702,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365740</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26659,6 +27804,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131852103</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26791,6 +27941,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124065</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26923,6 +28078,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124074</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -27060,6 +28220,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124077</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -27157,6 +28322,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131852478</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -27271,6 +28441,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98158609</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -27383,6 +28558,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354998</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -27510,6 +28690,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944676</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27642,6 +28827,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365741</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27739,6 +28929,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131851479</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27871,6 +29066,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124063</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27968,6 +29168,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131851241</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -28080,6 +29285,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126605219</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -28192,6 +29402,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753784</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -28313,6 +29528,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365747</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -28429,6 +29649,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910889</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -28532,6 +29757,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365744</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28647,6 +29877,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354154</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28765,6 +30000,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98158262</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28883,6 +30123,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99458021</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28994,6 +30239,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99462539</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -29121,6 +30371,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124052</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -29257,6 +30512,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231768</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -29393,6 +30653,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231793</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -29529,6 +30794,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231795</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -29635,6 +30905,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131845274</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -29736,6 +31011,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131845470</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -29862,6 +31142,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231774</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -29994,6 +31279,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231770</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -30105,6 +31395,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944670</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -30202,6 +31497,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131844576</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -30319,6 +31619,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231786</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -30431,6 +31736,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753763</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -30524,6 +31834,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131844464</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -30656,6 +31971,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231778</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -30768,6 +32088,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231788</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -30880,6 +32205,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231787</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -30987,6 +32317,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866861</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -31114,6 +32449,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124051</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -31221,6 +32561,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231776</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -31348,6 +32693,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231792</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -31475,6 +32825,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231794</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -31597,6 +32952,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910966</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -31704,6 +33064,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278597</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -31811,6 +33176,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910879</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -31918,6 +33288,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365726</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -32025,6 +33400,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365728</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -32152,6 +33532,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231789</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -32274,6 +33659,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944662</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -32381,6 +33771,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121221411</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -32495,6 +33890,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121221425</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -32622,6 +34022,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231785</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -32743,6 +34148,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124182917</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -32850,6 +34260,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126610206</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -32947,6 +34362,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129516556</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -33044,6 +34464,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131888519</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -33155,6 +34580,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365727</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -33272,6 +34702,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104335221</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -33389,6 +34824,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104337740</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -33534,6 +34974,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99505852</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -33654,6 +35099,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131696846</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -33766,6 +35216,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637881</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -33890,6 +35345,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866860</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -34002,6 +35462,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637887</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -34117,6 +35582,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99456502</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -34229,6 +35699,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121221017</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -34346,6 +35821,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231782</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -34458,6 +35938,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866858</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -34570,6 +36055,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866859</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -34677,6 +36167,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354229</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -34789,6 +36284,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354788</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -34901,6 +36401,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354834</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -35033,6 +36538,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944668</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -35160,6 +36670,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231771</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -35287,6 +36802,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365718</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -35399,6 +36919,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637856</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -35511,6 +37036,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637884</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -35623,6 +37153,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944672</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -35735,6 +37270,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637977</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -35847,6 +37387,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637985</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -35959,6 +37504,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637858</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -36071,6 +37621,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637885</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -36183,6 +37738,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637963</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -36295,6 +37855,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944643</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -36410,6 +37975,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129517893</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -36522,6 +38092,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637863</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -36634,6 +38209,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637888</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -36746,6 +38326,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637969</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -36858,6 +38443,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637899</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -36970,6 +38560,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637852</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -37082,6 +38677,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637851</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -37194,6 +38794,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637878</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -37306,6 +38911,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637959</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -37411,6 +39021,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131867113</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -37523,6 +39138,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637978</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -37642,6 +39262,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129516027</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -37754,6 +39379,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637868</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -37866,6 +39496,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637976</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -37993,6 +39628,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231781</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -38125,6 +39765,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944663</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -38252,6 +39897,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231775</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -38384,6 +40034,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365729</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -38500,6 +40155,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121222341</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -38612,6 +40272,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637869</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -38724,6 +40389,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637896</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -38841,6 +40511,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336525</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -38954,6 +40629,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336524</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -39071,6 +40751,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336526</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -39173,6 +40858,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354790</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -39287,6 +40977,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98155245</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -39394,6 +41089,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944659</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -39501,6 +41201,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944669</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -39613,6 +41318,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124045</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -39720,6 +41430,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124047</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -39827,6 +41542,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124048</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -39948,6 +41668,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231773</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -40060,6 +41785,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126609812</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -40171,6 +41901,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126609883</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -40282,6 +42017,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126609998</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -40393,6 +42133,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126610096</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -40504,6 +42249,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126610157</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -40615,6 +42365,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126610277</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -40741,6 +42496,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279306</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -40857,6 +42617,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910883</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -40973,6 +42738,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910884</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -41089,6 +42859,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910885</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -41196,6 +42971,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944660</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -41307,6 +43087,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131765108</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -41456,6 +43241,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99506210</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -41563,6 +43353,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124044</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -41687,6 +43482,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78796725</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -41803,6 +43603,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87150338</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -41920,6 +43725,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99454264</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -42017,6 +43827,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131888520</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -42114,6 +43929,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131888518</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -42216,8 +44036,379 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99477056</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>